--- a/public/datos/2.3_Tablas_y_filtros.xlsx
+++ b/public/datos/2.3_Tablas_y_filtros.xlsx
@@ -7,7 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Documentos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Enunciado_Caso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Parametros" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos_Crudos" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Consultas_Auditoria" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -429,17 +432,209 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sección</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Detalle del Requerimiento / Parámetros del Caso</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Código de Actividad</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Título del Caso</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Auditoría interactiva con Tablas de Excel y subtotales dinámicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Organización</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lácteos del Caribe S.A.S. - Sistema Integrado de Gestión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1. Situación Problema</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>En el Comité de Calidad mensual se requiere auditar el estado documental en tiempo real mediante filtros sin desconfigurar fórmulas ni rangos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2. Misión del Aprendiz</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Transformar el listado plano en una Tabla Oficial de Excel nombrada Tabla_SIG, agregar columna calculada estructurada, activar fila de subtotales y resolver 3 retos de auditoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Requerimiento 1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tabla Oficial: Convertir Datos_Crudos en Tabla con Ctrl+T y nombrarla Tabla_SIG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Requerimiento 2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Columna Estructurada: Crear columna Dias_Faltantes con fórmula de tabla: [@Fecha de vencimiento] - Parametros!$B$2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Requerimiento 3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fila de Subtotales: Activar totales dinámicos con SUBTOTALES para recuento y promedio de días de revisión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Requerimiento 4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Consultas de Comité: Filtrar la tabla y responder las 3 preguntas en la hoja Consultas_Auditoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Dificultad Clave / Regla Técnica</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Las fórmulas normales (SUMA/CONTAR) calculan filas ocultas. Comprueba que la fila de totales use SUBTOTALES (códigos 103/109) para reflejar solo lo filtrado.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Parámetro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fecha de corte de auditoría</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>46317</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,22 +660,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Tipo de proceso</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Versión</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Fecha de aprobación</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fecha de vencimiento</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Estado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Días de revisión</t>
         </is>
       </c>
     </row>
@@ -505,19 +710,27 @@
           <t>Direccionamiento estratégico</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>45332</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>46428</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -541,19 +754,27 @@
           <t>Direccionamiento estratégico</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>45672</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>46331</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -577,19 +798,27 @@
           <t>Direccionamiento estratégico</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="G4" s="2" t="n">
         <v>45170</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -613,19 +842,27 @@
           <t>Direccionamiento estratégico</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="G5" s="2" t="n">
         <v>45455</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="H5" s="2" t="n">
         <v>46325</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -649,19 +886,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="G6" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="H6" s="2" t="n">
         <v>46447</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J6" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -685,19 +930,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="G7" s="2" t="n">
         <v>45797</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="H7" s="2" t="n">
         <v>46527</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -721,19 +974,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="G8" s="2" t="n">
         <v>45153</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="H8" s="2" t="n">
         <v>45884</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -757,19 +1018,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="G9" s="2" t="n">
         <v>45575</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="H9" s="2" t="n">
         <v>46338</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -793,19 +1062,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="G10" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="H10" s="2" t="n">
         <v>46569</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -829,19 +1106,27 @@
           <t>Gestión de la calidad</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Estratégico</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="G11" s="2" t="n">
         <v>45311</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="H11" s="2" t="n">
         <v>46042</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -865,19 +1150,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="G12" s="2" t="n">
         <v>45601</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="H12" s="2" t="n">
         <v>46341</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -901,19 +1194,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="G13" s="2" t="n">
         <v>45702</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="H13" s="2" t="n">
         <v>46432</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -937,19 +1238,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="G14" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="H14" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J14" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="15">
@@ -973,19 +1282,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="G15" s="2" t="n">
         <v>45901</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="H15" s="2" t="n">
         <v>46631</v>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1009,19 +1326,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="G16" s="2" t="n">
         <v>45400</v>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="H16" s="2" t="n">
         <v>46130</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1045,19 +1370,27 @@
           <t>Producción</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="G17" s="2" t="n">
         <v>45719</v>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="H17" s="2" t="n">
         <v>46449</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J17" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1081,19 +1414,27 @@
           <t>Comercial y ventas</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="G18" s="2" t="n">
         <v>45512</v>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>46346</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J18" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -1117,19 +1458,27 @@
           <t>Comercial y ventas</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="G19" s="2" t="n">
         <v>45758</v>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="H19" s="2" t="n">
         <v>46488</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1153,19 +1502,27 @@
           <t>Comercial y ventas</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>4</v>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="G20" s="2" t="n">
         <v>45261</v>
       </c>
-      <c r="G20" s="2" t="n">
+      <c r="H20" s="2" t="n">
         <v>45992</v>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1189,19 +1546,27 @@
           <t>Comercial y ventas</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="G21" s="2" t="n">
         <v>45814</v>
       </c>
-      <c r="G21" s="2" t="n">
+      <c r="H21" s="2" t="n">
         <v>46544</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1225,19 +1590,27 @@
           <t>Logística y distribución</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="G22" s="2" t="n">
         <v>45434</v>
       </c>
-      <c r="G22" s="2" t="n">
+      <c r="H22" s="2" t="n">
         <v>46164</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1261,19 +1634,27 @@
           <t>Logística y distribución</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="G23" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="G23" s="2" t="n">
+      <c r="H23" s="2" t="n">
         <v>46618</v>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -1297,19 +1678,27 @@
           <t>Logística y distribución</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="G24" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="G24" s="2" t="n">
+      <c r="H24" s="2" t="n">
         <v>46327</v>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1333,19 +1722,27 @@
           <t>Logística y distribución</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Misional</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="G25" s="2" t="n">
         <v>45666</v>
       </c>
-      <c r="G25" s="2" t="n">
+      <c r="H25" s="2" t="n">
         <v>46396</v>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -1369,19 +1766,27 @@
           <t>Talento humano</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>4</v>
       </c>
-      <c r="F26" s="2" t="n">
+      <c r="G26" s="2" t="n">
         <v>45488</v>
       </c>
-      <c r="G26" s="2" t="n">
+      <c r="H26" s="2" t="n">
         <v>46218</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J26" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="27">
@@ -1405,19 +1810,27 @@
           <t>Talento humano</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" s="2" t="n">
+      <c r="G27" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="G27" s="2" t="n">
+      <c r="H27" s="2" t="n">
         <v>46420</v>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J27" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1441,19 +1854,27 @@
           <t>Talento humano</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="2" t="n">
+      <c r="G28" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="G28" s="2" t="n">
+      <c r="H28" s="2" t="n">
         <v>46336</v>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1477,19 +1898,27 @@
           <t>Talento humano</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="2" t="n">
+      <c r="G29" s="2" t="n">
         <v>46032</v>
       </c>
-      <c r="G29" s="2" t="n">
+      <c r="H29" s="2" t="n">
         <v>46387</v>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J29" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1513,19 +1942,27 @@
           <t>Compras</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
         <v>3</v>
       </c>
-      <c r="F30" s="2" t="n">
+      <c r="G30" s="2" t="n">
         <v>45241</v>
       </c>
-      <c r="G30" s="2" t="n">
+      <c r="H30" s="2" t="n">
         <v>45972</v>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J30" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -1549,19 +1986,27 @@
           <t>Compras</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
         <v>5</v>
       </c>
-      <c r="F31" s="2" t="n">
+      <c r="G31" s="2" t="n">
         <v>45782</v>
       </c>
-      <c r="G31" s="2" t="n">
+      <c r="H31" s="2" t="n">
         <v>46512</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1585,19 +2030,27 @@
           <t>Compras</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="2" t="n">
+      <c r="G32" s="2" t="n">
         <v>45638</v>
       </c>
-      <c r="G32" s="2" t="n">
+      <c r="H32" s="2" t="n">
         <v>46368</v>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1621,19 +2074,27 @@
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
         <v>2</v>
       </c>
-      <c r="F33" s="2" t="n">
+      <c r="G33" s="2" t="n">
         <v>45376</v>
       </c>
-      <c r="G33" s="2" t="n">
+      <c r="H33" s="2" t="n">
         <v>46106</v>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J33" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1657,19 +2118,27 @@
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="2" t="n">
+      <c r="G34" s="2" t="n">
         <v>45845</v>
       </c>
-      <c r="G34" s="2" t="n">
+      <c r="H34" s="2" t="n">
         <v>46575</v>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -1693,19 +2162,27 @@
           <t>Mantenimiento</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="2" t="n">
+      <c r="G35" s="2" t="n">
         <v>45945</v>
       </c>
-      <c r="G35" s="2" t="n">
+      <c r="H35" s="2" t="n">
         <v>46334</v>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -1729,19 +2206,27 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="2" t="n">
+      <c r="G36" s="2" t="n">
         <v>45734</v>
       </c>
-      <c r="G36" s="2" t="n">
+      <c r="H36" s="2" t="n">
         <v>46464</v>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -1765,19 +2250,27 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="2" t="n">
+      <c r="G37" s="2" t="n">
         <v>45444</v>
       </c>
-      <c r="G37" s="2" t="n">
+      <c r="H37" s="2" t="n">
         <v>46174</v>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J37" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="38">
@@ -1801,19 +2294,27 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="2" t="n">
+      <c r="G38" s="2" t="n">
         <v>45350</v>
       </c>
-      <c r="G38" s="2" t="n">
+      <c r="H38" s="2" t="n">
         <v>46344</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Por vencer</t>
         </is>
+      </c>
+      <c r="J38" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="39">
@@ -1837,19 +2338,27 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="F39" s="2" t="n">
+      <c r="G39" s="2" t="n">
         <v>45877</v>
       </c>
-      <c r="G39" s="2" t="n">
+      <c r="H39" s="2" t="n">
         <v>46607</v>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Vigente</t>
         </is>
+      </c>
+      <c r="J39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -1873,19 +2382,27 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="2" t="n">
+      <c r="G40" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="G40" s="2" t="n">
+      <c r="H40" s="2" t="n">
         <v>45950</v>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Vencido</t>
         </is>
+      </c>
+      <c r="J40" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -1909,18 +2426,92 @@
           <t>Seguridad y salud en el trabajo</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Apoyo</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
         <v>3</v>
       </c>
-      <c r="F41" s="2" t="n">
+      <c r="G41" s="2" t="n">
         <v>45687</v>
       </c>
-      <c r="G41" s="2" t="n">
+      <c r="H41" s="2" t="n">
         <v>46417</v>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Vigente</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pregunta de Auditoría en Comité</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Tu Respuesta Formulada / Filtrada</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>¿Cuántos documentos en estado 'Vencido' pertenecen a procesos de tipo 'Misional'?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>¿Cuál es el promedio de días de revisión para los documentos del proceso 'Seguridad y salud en el trabajo'?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Aplica un filtro por Estado = 'Por vencer'. ¿Qué valor dinámico muestra la fila de subtotales para el recuento total?</t>
         </is>
       </c>
     </row>
